--- a/_attic/data/0520 권동환 사원님 재고/진한파랑_등록대상_20260522.xlsx
+++ b/_attic/data/0520 권동환 사원님 재고/진한파랑_등록대상_20260522.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ERP\_attic\data\0520 권동환 사원님 재고\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\nas\Nas 문서\03. 생산부\20. 조립공정\1. 김건호 back up\창고 재고파일\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61A552A3-9FBB-429F-B2C6-B9477645A119}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29553642-DEAD-41FA-AC0C-147716287825}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="진한파랑_등록대상" sheetId="1" r:id="rId1"/>
@@ -643,7 +643,7 @@
         <v>13</v>
       </c>
       <c r="C6" s="2">
-        <v>4</v>
+        <v>46</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>46</v>
@@ -660,7 +660,7 @@
         <v>15</v>
       </c>
       <c r="C7" s="2">
-        <v>4</v>
+        <v>46</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>46</v>
@@ -694,7 +694,7 @@
         <v>19</v>
       </c>
       <c r="C9" s="2">
-        <v>34</v>
+        <v>348</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>47</v>
@@ -711,7 +711,7 @@
         <v>20</v>
       </c>
       <c r="C10" s="2">
-        <v>34</v>
+        <v>348</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>47</v>
@@ -864,7 +864,7 @@
         <v>38</v>
       </c>
       <c r="C19" s="2">
-        <v>34678</v>
+        <v>3</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>45</v>
@@ -881,7 +881,7 @@
         <v>40</v>
       </c>
       <c r="C20" s="2">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>45</v>
